--- a/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35F8AB53-39AE-4D39-AF85-2EE2F533E6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{78B6C0ED-69FF-4850-B0D5-39A2137C473D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2705,7 +2705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{885BE1F7-3847-4032-AE4F-0F851AC6D611}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD703699-E76E-4502-8E4B-D2D802840050}">
   <dimension ref="B9:E263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78B6C0ED-69FF-4850-B0D5-39A2137C473D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF60256F-3D84-4A25-9586-F355700DC11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2705,7 +2705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD703699-E76E-4502-8E4B-D2D802840050}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0121CDC7-7887-4791-8C18-A2981E1368DF}">
   <dimension ref="B9:E263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF60256F-3D84-4A25-9586-F355700DC11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE34AEFA-066C-4889-86AE-20FE1C41003A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2705,7 +2705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0121CDC7-7887-4791-8C18-A2981E1368DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7392F1-BA22-4D8B-A269-4C6E7982AF80}">
   <dimension ref="B9:E263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE34AEFA-066C-4889-86AE-20FE1C41003A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D7DD0BA-C32B-4083-A7D5-1DB920020A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2705,7 +2705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7392F1-BA22-4D8B-A269-4C6E7982AF80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFAE1B6E-2549-43BB-A452-D0C825114D49}">
   <dimension ref="B9:E263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D7DD0BA-C32B-4083-A7D5-1DB920020A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B36A66D-B172-4D7B-8304-0AF3FF4F608F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2705,7 +2705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFAE1B6E-2549-43BB-A452-D0C825114D49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A35A72-760B-4A78-8A26-EDA664E9EC15}">
   <dimension ref="B9:E263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B36A66D-B172-4D7B-8304-0AF3FF4F608F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC7251D0-4122-47AC-BD6E-CBAACBD71600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2705,7 +2705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A35A72-760B-4A78-8A26-EDA664E9EC15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC73BF75-7D76-4591-83A1-0BAD82B46C8C}">
   <dimension ref="B9:E263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC7251D0-4122-47AC-BD6E-CBAACBD71600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07FDA030-D775-43A5-A52B-49A7F4790B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2705,7 +2705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC73BF75-7D76-4591-83A1-0BAD82B46C8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC734DFC-DFD6-4FFC-8A42-E30E75258C32}">
   <dimension ref="B9:E263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07FDA030-D775-43A5-A52B-49A7F4790B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{456338F1-7AFC-4B5E-A35A-02EDDB356DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2705,7 +2705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC734DFC-DFD6-4FFC-8A42-E30E75258C32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A884CFD2-6101-42F2-8710-038F4EFD8322}">
   <dimension ref="B9:E263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_IDN_grids_kan/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{456338F1-7AFC-4B5E-A35A-02EDDB356DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{563D7A68-FB01-4791-93D7-339D6A0AF25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2705,7 +2705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A884CFD2-6101-42F2-8710-038F4EFD8322}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D182FFA1-7023-4F61-9C37-930DD90DF782}">
   <dimension ref="B9:E263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
